--- a/preview/pr-13/CodeSystem-dem-einkommen.xlsx
+++ b/preview/pr-13/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:34:58+00:00</t>
+    <t>2026-09-30T07:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,31 +141,31 @@
     <t>band-niedrig</t>
   </si>
   <si>
-    <t>Bis zu 2.300 € pro Monat</t>
+    <t>Up to €2,300 a month</t>
   </si>
   <si>
     <t>band-mittel</t>
   </si>
   <si>
-    <t>Zwischen 2.300 € und 5.200 € pro Monat</t>
+    <t>Between €2,300 and €5,200 a month</t>
   </si>
   <si>
     <t>band-hoch</t>
   </si>
   <si>
-    <t>5.200 € pro Monat oder mehr</t>
+    <t>€5,200 a month or more</t>
   </si>
   <si>
     <t>weiss-nicht</t>
   </si>
   <si>
-    <t>Ich weiss es nicht</t>
+    <t>Don't know</t>
   </si>
   <si>
     <t>keine-angabe</t>
   </si>
   <si>
-    <t>Möchte ich nicht sagen</t>
+    <t>Prefer not to say</t>
   </si>
 </sst>
 </file>

--- a/preview/pr-13/CodeSystem-dem-einkommen.xlsx
+++ b/preview/pr-13/CodeSystem-dem-einkommen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T07:33:31+00:00</t>
+    <t>2026-09-30T08:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/CodeSystem-dem-einkommen.xlsx
+++ b/preview/pr-13/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:17:00+00:00</t>
+    <t>2026-09-30T08:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
